--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,22 +419,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -457,10 +445,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1877</v>
+        <v>0.1888</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
@@ -471,7 +459,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2503</v>
+        <v>0.2517</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
@@ -485,10 +473,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3754</v>
+        <v>0.3776</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -499,10 +487,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -513,10 +501,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6257</v>
+        <v>0.6294</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -527,7 +515,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7508</v>
+        <v>0.7552</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -541,7 +529,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>0.9385</v>
+        <v>0.944</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -555,7 +543,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>1.2513</v>
+        <v>1.2587</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -575,96 +563,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:W2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>picos_con_sep_menor</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>k_usado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>k_automatico</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hay_meseta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>meseta_motivo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>meseta_k_rango</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>conteo_reportable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
@@ -677,55 +690,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.66097156017238</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="C2" t="n">
         <v>1846</v>
       </c>
       <c r="D2" t="n">
-        <v>62.20295232936078</v>
+        <v>62.2</v>
       </c>
       <c r="E2" t="n">
         <v>-1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06256572000005434</v>
+        <v>0.06293637000004557</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1016419775900214</v>
+        <v>0.101862030907396</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10.58630191404839</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.5390999999999622</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.4158069069727333</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7.085642232580338</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.6068580715059824</v>
+        <v>10</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>el conteo no se estabiliza en ningun tramo con 0 falsos: no hay meseta</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="b">
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>73.02972430877819</v>
+        <v>0.5</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04768679862516478</v>
+        <v>0.696049999999957</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.407493235251055</v>
+        <v>0.334685824011558</v>
       </c>
       <c r="R2" t="n">
-        <v>8.375411034219248</v>
+        <v>4.64665025068525</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.5999999999999659</v>
+      </c>
+      <c r="T2" t="n">
+        <v>48.0835893989769</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.08363875790983381</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.011272284424755</v>
+      </c>
+      <c r="W2" t="n">
+        <v>12.0161996853443</v>
       </c>
     </row>
   </sheetData>
@@ -739,21 +767,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
@@ -764,10 +792,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12.81144817623691</v>
+        <v>12.88</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5390999999999622</v>
+        <v>0.643799999999942</v>
       </c>
     </row>
     <row r="3">
@@ -775,21 +803,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>13.31716323582521</v>
+        <v>13.38</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6435999999999922</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>33.98405200433369</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.5253999999999905</v>
+        <v>0.748299999999972</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_491_EXP5_CTR" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -563,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,6 +683,96 @@
           <t>cociente_robusto_pct</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -754,6 +845,56 @@
       </c>
       <c r="W2" t="n">
         <v>12.0161996853443</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.2724282403004153</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.2622-0.2827</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>0.2666666666666693</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.93333333333333</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.56666666666667</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -812,4 +953,227 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>380</v>
+      </c>
+      <c r="C2" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.643799999999942</v>
+      </c>
+      <c r="E2" t="n">
+        <v>255.5437864962033</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2519333413765109</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12.46716332378224</v>
+      </c>
+      <c r="I2" t="n">
+        <v>13</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.4128366762177613</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2666666666666693</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.93333333333333</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>395</v>
+      </c>
+      <c r="C3" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.748299999999972</v>
+      </c>
+      <c r="E3" t="n">
+        <v>255.4595044903317</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2929231392243198</v>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.08329314579147251</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.56666666666667</v>
+      </c>
+      <c r="R3" t="b">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13.4766586291583</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,110 +446,320 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1888</v>
+        <v>0.2039</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.2243</v>
+      </c>
+      <c r="C3" t="n">
         <v>4</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.2517</v>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3776</v>
+        <v>0.2468</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.2714</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6294</v>
+        <v>0.2986</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>0.7552</v>
+        <v>0.3285</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>0.944</v>
+        <v>0.3613</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>1.2587</v>
+        <v>0.3974</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4372</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7.074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7.781</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8.558999999999999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.414999999999999</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11.392</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12.532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13.785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9371</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15.163</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.0307</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.1339</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18.348</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.2472</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20.182</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.3719</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22.201</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.5092</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24.421</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1.6601</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -564,7 +774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -773,6 +983,61 @@
           <t>cinetica_motivo</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida_pct</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>fotogramas_low_quality</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>eventos_junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>win_s_usado</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>win_s_automatico</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>duracion_evento_max_s</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>ventana_corta</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>conteo_por_ventana</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>conteo_estable_ventana</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>mesetas</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -793,107 +1058,160 @@
         <v>-1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06293637000004557</v>
+        <v>0.06797720999996008</v>
       </c>
       <c r="G2" t="n">
-        <v>0.101862030907396</v>
+        <v>0.1026783373048835</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>10.357</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>el conteo no se estabiliza en ningun tramo con 0 falsos: no hay meseta</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>meseta de 2 eventos en k=7.781..13.785 (x1.77) con 0 falsos de control</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>7.781-13.785</t>
+        </is>
+      </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5</v>
+        <v>20.95000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.696049999999957</v>
+        <v>1.015199999999993</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.334685824011558</v>
+        <v>0.5006994040343926</v>
       </c>
       <c r="R2" t="n">
-        <v>4.64665025068525</v>
+        <v>6.896253936748217</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5999999999999659</v>
+        <v>0.6333333333332973</v>
       </c>
       <c r="T2" t="n">
-        <v>48.0835893989769</v>
+        <v>49.32027226501143</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08363875790983381</v>
+        <v>-0.05636949511709114</v>
       </c>
       <c r="V2" t="n">
-        <v>2.011272284424755</v>
+        <v>1.344748110647621</v>
       </c>
       <c r="W2" t="n">
-        <v>12.0161996853443</v>
+        <v>-5.552550740454248</v>
       </c>
       <c r="X2" t="n">
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2724282403004153</v>
+        <v>0.3974555803223884</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.2622-0.2827</t>
+          <t>0.3892-0.4058</t>
         </is>
       </c>
       <c r="AA2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC2" t="b">
         <v>1</v>
       </c>
-      <c r="AB2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>0.5698358797361323</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.5632-0.5765</t>
+        </is>
+      </c>
       <c r="AF2" t="n">
-        <v>0.2666666666666693</v>
+        <v>0.3858333333333306</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.93333333333333</v>
+        <v>1.067500000000003</v>
       </c>
       <c r="AH2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AJ2" t="b">
         <v>1</v>
       </c>
-      <c r="AI2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
+      <c r="AK2" t="n">
+        <v>0.4665204478323792</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.4594-0.4737</t>
+        </is>
+      </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.56666666666667</v>
+        <v>0.6483333333333361</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>TTP: el conteo de eventos no es reportable; RT50: el conteo de eventos no es reportable</t>
+          <t>TTP y RT50 medibles</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1.033333333333275</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2.33 s: 2 | 3.1 s: 2 | 4.65 s: 2</t>
+        </is>
+      </c>
+      <c r="AY2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>2 ev en k=7.781-13.785</t>
         </is>
       </c>
     </row>
@@ -908,7 +1226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,16 +1245,24 @@
           <t>amplitud_px</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>12.88</v>
+        <v>13.01333333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.643799999999942</v>
+        <v>0.9731000000000449</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -944,10 +1270,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>13.38</v>
+        <v>33.96333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>0.748299999999972</v>
+        <v>1.057299999999941</v>
+      </c>
+      <c r="D3" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1076,102 +1405,130 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C2" t="n">
-        <v>12.88</v>
+        <v>13.01333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.643799999999942</v>
+        <v>0.9731000000000449</v>
       </c>
       <c r="E2" t="n">
-        <v>255.5437864962033</v>
+        <v>255.5012334789002</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2519333413765109</v>
+        <v>0.3808592180751274</v>
       </c>
       <c r="G2" t="n">
+        <v>19</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12.43020369119965</v>
+      </c>
+      <c r="I2" t="n">
         <v>18</v>
       </c>
-      <c r="H2" t="n">
-        <v>12.46716332378224</v>
-      </c>
-      <c r="I2" t="n">
-        <v>13</v>
-      </c>
       <c r="J2" t="n">
-        <v>0.4128366762177613</v>
+        <v>0.5831296421336845</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2666666666666693</v>
+        <v>0.36666666666666</v>
       </c>
       <c r="L2" t="n">
-        <v>0.93333333333333</v>
+        <v>1.06666666666667</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4522326412145627</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.6666666666666696</v>
+      </c>
       <c r="R2" t="b">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>13.48387606461087</v>
+      </c>
+      <c r="T2" t="n">
+        <v>33</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.053672373411223</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>395</v>
+        <v>1008</v>
       </c>
       <c r="C3" t="n">
-        <v>13.38</v>
+        <v>33.96333333333334</v>
       </c>
       <c r="D3" t="n">
-        <v>0.748299999999972</v>
+        <v>1.057299999999941</v>
       </c>
       <c r="E3" t="n">
-        <v>255.4595044903317</v>
+        <v>255.3544353489148</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2929231392243198</v>
+        <v>0.4140519425696493</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="H3" t="n">
+        <v>33.40679121599476</v>
+      </c>
+      <c r="I3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5565421173385801</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.4050000000000011</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.068333333333335</v>
+      </c>
       <c r="M3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08329314579147251</v>
+        <v>0.4808082544501957</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.56666666666667</v>
+        <v>0.6300000000000026</v>
       </c>
       <c r="R3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>13.4766586291583</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+        <v>34.45736019824969</v>
+      </c>
+      <c r="T3" t="n">
+        <v>32</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.05056898225493</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_491_EXP5_CTR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="estab_Video_491_EXP5_CTRL1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen_Video_491_EXP5_CTR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="eventos_Video_491_EXP5_CTR" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="cinetica_Video_491_EXP5_CTR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cin_grupos_Video_491_EXP5_C" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +21,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +49,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,22 +433,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -774,268 +787,303 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:BG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_grupo_principal</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mesetas</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_sup_px</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_inf_px</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>cociente_ruido_bordes</t>
         </is>
       </c>
     </row>
@@ -1115,104 +1163,127 @@
       <c r="W2" t="n">
         <v>-5.552550740454248</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>5</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.3974555803223884</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.3892-0.4058</t>
         </is>
       </c>
-      <c r="AA2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE2" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC2" t="b">
+      <c r="AF2" t="b">
         <v>1</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>0.5698358797361323</v>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>0.5632-0.5765</t>
         </is>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>0.3858333333333306</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>1.067500000000003</v>
       </c>
-      <c r="AH2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI2" t="n">
+      <c r="AK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AJ2" t="b">
+      <c r="AN2" t="b">
         <v>1</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AO2" t="n">
         <v>0.4665204478323792</v>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>0.4594-0.4737</t>
         </is>
       </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
         <v>0.6483333333333361</v>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
       </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
       <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AU2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1.033333333333275</v>
-      </c>
-      <c r="AW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>2.33 s: 2 | 3.1 s: 2 | 4.65 s: 2</t>
-        </is>
       </c>
       <c r="AY2" t="b">
         <v>1</v>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ2" t="n">
+        <v>1.033333333333275</v>
+      </c>
+      <c r="BA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>2.33 s: 2 | 3.1 s: 2 | 4.65 s: 2</t>
+        </is>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BD2" t="inlineStr">
         <is>
           <t>2 ev en k=7.781-13.785</t>
         </is>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.08903012999998476</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0.06671699999993931</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1.33444444444543</v>
       </c>
     </row>
   </sheetData>
@@ -1230,22 +1301,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
         </is>
@@ -1294,107 +1365,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -1528,6 +1599,210 @@
       </c>
       <c r="U3" t="n">
         <v>1.05056898225493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3974555803223884</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.3892-0.4058</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5698358797361323</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5632-0.5765</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.3858333333333306</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.067500000000003</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4665204478323792</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.4594-0.4737</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6483333333333361</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TTP y RT50 medibles</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/contracciones.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,22 +421,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -787,301 +775,306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG2"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>eventos_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1252,37 +1245,40 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3.1</v>
       </c>
-      <c r="AY2" t="b">
+      <c r="AZ2" t="b">
         <v>1</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BA2" t="n">
         <v>1.033333333333275</v>
       </c>
-      <c r="BA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>2.33 s: 2 | 3.1 s: 2 | 4.65 s: 2</t>
         </is>
       </c>
-      <c r="BC2" t="b">
+      <c r="BD2" t="b">
         <v>1</v>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>2 ev en k=7.781-13.785</t>
         </is>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>0.08903012999998476</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BG2" t="n">
         <v>0.06671699999993931</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>1.33444444444543</v>
       </c>
     </row>
@@ -1297,28 +1293,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>junto_al_borde</t>
         </is>
       </c>
     </row>
@@ -1335,6 +1336,9 @@
       <c r="D2" t="b">
         <v>0</v>
       </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1347,6 +1351,9 @@
         <v>1.057299999999941</v>
       </c>
       <c r="D3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1365,107 +1372,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -1616,112 +1623,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
